--- a/diccionario.xlsx
+++ b/diccionario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Indatech\Desktop\Sistema Automatizacion Finanzas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57289669-96BE-4687-B5AC-2DBE04C74356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0BD89A-BC7E-400B-8F76-4B8BFE1B3B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{A9583FC7-4D3D-4BDA-AE3D-8A8227054763}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{A9583FC7-4D3D-4BDA-AE3D-8A8227054763}"/>
   </bookViews>
   <sheets>
     <sheet name="CATEGORIA" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="139">
   <si>
     <t xml:space="preserve">SALDO INICIAL </t>
   </si>
@@ -407,13 +407,58 @@
     <t>APORTE 20% BP</t>
   </si>
   <si>
-    <t>HOLA</t>
-  </si>
-  <si>
-    <t>ADROS</t>
-  </si>
-  <si>
     <t>COBRANZA FINANCIAMIENTO</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA ENTRE CTAS</t>
+  </si>
+  <si>
+    <t>APORTE FIDEICOMISO</t>
+  </si>
+  <si>
+    <t>CONTINUIDAD</t>
+  </si>
+  <si>
+    <t>TICKET ALIMENTACION</t>
+  </si>
+  <si>
+    <t>BONO Y ALIMENTACION</t>
+  </si>
+  <si>
+    <t>TRASPASO DESDE LA CTA 1966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRASPASO DESDE LA CTA </t>
+  </si>
+  <si>
+    <t>ADELANTO DE BONO DE LEALTAD ENERO</t>
+  </si>
+  <si>
+    <t>BONO CRITICO</t>
+  </si>
+  <si>
+    <t>ALIADO</t>
+  </si>
+  <si>
+    <t>SIM CARD</t>
+  </si>
+  <si>
+    <t>TRASPASO ENTRE CUENTAS</t>
+  </si>
+  <si>
+    <t>TRASPASO</t>
+  </si>
+  <si>
+    <t>APORTE  BANCO ING</t>
+  </si>
+  <si>
+    <t>APORTE DE LOS BANCOS - COMPRA DE POS</t>
+  </si>
+  <si>
+    <t>APORTE BANCO EG</t>
+  </si>
+  <si>
+    <t>COMPRA POS - BANCO</t>
   </si>
 </sst>
 </file>
@@ -537,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -573,6 +618,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -887,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE9443F-E15E-4C56-A6CD-A01660DB3178}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="158.5703125" customWidth="1"/>
@@ -1291,10 +1339,114 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1305,7 +1457,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F7FE5DE-51AC-4617-BB94-0E66FF4A7B9B}">
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="74.42578125" customWidth="1"/>
@@ -1972,10 +2124,42 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B84" t="s">
-        <v>122</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>130</v>
+      </c>
+      <c r="B86" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>136</v>
+      </c>
+      <c r="B87" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B88" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/diccionario.xlsx
+++ b/diccionario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Indatech\Desktop\Sistema Automatizacion Finanzas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0BD89A-BC7E-400B-8F76-4B8BFE1B3B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993FF303-6F2C-4DC8-9EE2-2DC4A2A1FB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{A9583FC7-4D3D-4BDA-AE3D-8A8227054763}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="AREA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">AREA!$A$1:$B$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CATEGORIA!$A$1:$C$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">AREA!$A$1:$B$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CATEGORIA!$A$1:$C$123</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="203">
   <si>
     <t xml:space="preserve">SALDO INICIAL </t>
   </si>
@@ -89,9 +89,6 @@
     <t>AYUDA EDUCATIVA</t>
   </si>
   <si>
-    <t>V271192769 NAVIDAD CON PLATCO RAFAEL ANTONIO VARGAS LEGED SERIAL NEC900206064</t>
-  </si>
-  <si>
     <t>PALABRA CLAVE</t>
   </si>
   <si>
@@ -161,9 +158,6 @@
     <t>REINTEGRO PROVEEDOR</t>
   </si>
   <si>
-    <t>REINTEGRO SIMCARD</t>
-  </si>
-  <si>
     <t>NOMINA</t>
   </si>
   <si>
@@ -176,24 +170,6 @@
     <t>BONO DE TRANSPORTE</t>
   </si>
   <si>
-    <t>REINTEGRO RETENCION IVA CONTINUIDAD OPERATIVA</t>
-  </si>
-  <si>
-    <t>REINTEGRO RETENCION IVA SERVICIO ESPECIALIZADO</t>
-  </si>
-  <si>
-    <t>REINTEGRO RETENCION IVA SIMCARD</t>
-  </si>
-  <si>
-    <t>REINTEGRO RETENCION ISLR CONTINUIDAD OPERATIVA</t>
-  </si>
-  <si>
-    <t>REINTEGRO RETENCION ISLR SERVICIO ESPECIALIZADO</t>
-  </si>
-  <si>
-    <t>REINTEGRO RETENCION ISLR SIMCARD</t>
-  </si>
-  <si>
     <t>REPORTE VENTA</t>
   </si>
   <si>
@@ -206,9 +182,6 @@
     <t>BANCO MERCANTIL</t>
   </si>
   <si>
-    <t>BANCO PROVINCIAL</t>
-  </si>
-  <si>
     <t>OBSERVACION</t>
   </si>
   <si>
@@ -233,9 +206,6 @@
     <t>ERNESTO JOSE LOPEZ SEVILLA</t>
   </si>
   <si>
-    <t>OPERACIONES/ COMERCIAL</t>
-  </si>
-  <si>
     <t>SERGIO LUIS MARCANO BALZA</t>
   </si>
   <si>
@@ -459,13 +429,235 @@
   </si>
   <si>
     <t>COMPRA POS - BANCO</t>
+  </si>
+  <si>
+    <t>ESPECIALIZADO</t>
+  </si>
+  <si>
+    <t>BONO</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA ENTRE CTRAS</t>
+  </si>
+  <si>
+    <t>APORTE DE FIDEICOMISO</t>
+  </si>
+  <si>
+    <t>COBRO DIFERENCIA</t>
+  </si>
+  <si>
+    <t>FIDECOMISO</t>
+  </si>
+  <si>
+    <t>REVERSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIQUIDACION </t>
+  </si>
+  <si>
+    <t>PAGO SUDEBAN</t>
+  </si>
+  <si>
+    <t>APORTE BANCO PROVINCIAL</t>
+  </si>
+  <si>
+    <t>APORTE BANCO MERCANTIL</t>
+  </si>
+  <si>
+    <t>PAGO APORTES AL IVSS</t>
+  </si>
+  <si>
+    <t>PAGO APORTES AL  FAOV</t>
+  </si>
+  <si>
+    <t>PAGO APORTE INCES</t>
+  </si>
+  <si>
+    <t>PAGO DE APORTE PENSIONADO</t>
+  </si>
+  <si>
+    <t>PAGO APORTES AL BANAVIH</t>
+  </si>
+  <si>
+    <t>APORTE BP</t>
+  </si>
+  <si>
+    <t>APORTE BM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COBRO FACTURA  BANCO MERCANTIL </t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>REIN-VEN</t>
+  </si>
+  <si>
+    <t>REIN-RET-VEN</t>
+  </si>
+  <si>
+    <t>REIN-ESP</t>
+  </si>
+  <si>
+    <t>REIN-RET-ESP</t>
+  </si>
+  <si>
+    <t>REIN-SIM</t>
+  </si>
+  <si>
+    <t>REIN-RET-SIM</t>
+  </si>
+  <si>
+    <t>REIN-CONT</t>
+  </si>
+  <si>
+    <t>DEBITO APORTE DE BANCO MERCANTIL</t>
+  </si>
+  <si>
+    <t>REIN-FIN</t>
+  </si>
+  <si>
+    <t>REIN-RET-CONT</t>
+  </si>
+  <si>
+    <t>INSTAPAGOS CROSSCONEXION</t>
+  </si>
+  <si>
+    <t>INTELIGENSA</t>
+  </si>
+  <si>
+    <t>POSCOMERCIAL</t>
+  </si>
+  <si>
+    <t>CONSULTORA ALCA</t>
+  </si>
+  <si>
+    <t>VE PAGOS</t>
+  </si>
+  <si>
+    <t>INSTAPAGOS</t>
+  </si>
+  <si>
+    <t>ISLR</t>
+  </si>
+  <si>
+    <t>IVA</t>
+  </si>
+  <si>
+    <t>FRANQUICIA</t>
+  </si>
+  <si>
+    <t>LOCTI</t>
+  </si>
+  <si>
+    <t>REINTEGRO DE LUIS MOLINA POR  VIATICOS</t>
+  </si>
+  <si>
+    <t>Inversion- Compra de POS</t>
+  </si>
+  <si>
+    <t>SERV. ESPEC</t>
+  </si>
+  <si>
+    <t>PAGO DEVUELTO CLIENTE</t>
+  </si>
+  <si>
+    <t>COMPRA DE POS-</t>
+  </si>
+  <si>
+    <t>COMPRA DE POS</t>
+  </si>
+  <si>
+    <t>TX BANCO MERCANTIL</t>
+  </si>
+  <si>
+    <t>TX BANCO PROVINCIAL</t>
+  </si>
+  <si>
+    <t>PAGO VA TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>PAGO MEMORYTECH</t>
+  </si>
+  <si>
+    <t>PAGO TECNOLOGIA AVA</t>
+  </si>
+  <si>
+    <t>JORNADA ESPECIAL</t>
+  </si>
+  <si>
+    <t>RETENCION IVA</t>
+  </si>
+  <si>
+    <t>RETENCIONES IVA</t>
+  </si>
+  <si>
+    <t>PAGO DEL 25% DE IVA</t>
+  </si>
+  <si>
+    <t>COBRO TX</t>
+  </si>
+  <si>
+    <t>PAGO TX</t>
+  </si>
+  <si>
+    <t>REPOSICION DE FONDOS</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA PARA REINTEGRO</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DESDE LA 6377</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DESDE LA 4041</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DESDE LA 1966</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DESDE LA 4149</t>
+  </si>
+  <si>
+    <t>PAGO FACTURA</t>
+  </si>
+  <si>
+    <t>PAGO APORTES LEY DE PENSIONES</t>
+  </si>
+  <si>
+    <t>INVERSION - COMPRA DE POS</t>
+  </si>
+  <si>
+    <t>TICKET DE ALIMENTACION</t>
+  </si>
+  <si>
+    <t>MERCANITL SEGUROS</t>
+  </si>
+  <si>
+    <t>EDWARD</t>
+  </si>
+  <si>
+    <t>CARTONAJE MARCANO</t>
+  </si>
+  <si>
+    <t>OPERACIONES / COMERCIAL</t>
+  </si>
+  <si>
+    <t>COBRANZA CONTINUIDAD</t>
+  </si>
+  <si>
+    <t>COBRANZA CONTINUIDAD OPERATIVA</t>
+  </si>
+  <si>
+    <t>COMPRA SIM CARD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,8 +678,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -496,14 +707,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -579,50 +784,61 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="20% - Énfasis1" xfId="1" builtinId="30"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -935,529 +1151,1014 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE9443F-E15E-4C56-A6CD-A01660DB3178}">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="158.5703125" customWidth="1"/>
-    <col min="2" max="2" width="57" customWidth="1"/>
+    <col min="1" max="1" width="158.5703125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="57" style="10" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="5"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="19">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="19">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="4"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B57" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B67" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B70" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B72" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B74" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B76" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B88" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B92" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B93" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="B98" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B103" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B104" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B105" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B109" s="24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B111" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B120" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B121" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="B122" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>125</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>127</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>128</v>
-      </c>
-      <c r="B56" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>129</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>132</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>133</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>134</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>135</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>137</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>138</v>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B123" s="24" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C49" xr:uid="{DEE9443F-E15E-4C56-A6CD-A01660DB3178}"/>
+  <autoFilter ref="A1:C123" xr:uid="{DEE9443F-E15E-4C56-A6CD-A01660DB3178}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B123">
+    <sortCondition ref="A1:A123"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F7FE5DE-51AC-4617-BB94-0E66FF4A7B9B}">
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="74.42578125" customWidth="1"/>
@@ -1465,229 +2166,229 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>55</v>
+      <c r="A1" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>100</v>
+      <c r="A28" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
         <v>61</v>
@@ -1695,475 +2396,745 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B48" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>111</v>
+        <v>38</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B57" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="B59" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B63" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B64" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="B70" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="B74" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="B79" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="B80" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="B84" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="13" t="s">
-        <v>138</v>
+      <c r="A88" t="s">
+        <v>76</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>180</v>
+      </c>
+      <c r="B89" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>195</v>
+      </c>
+      <c r="B90" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>196</v>
+      </c>
+      <c r="B91" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>197</v>
+      </c>
+      <c r="B92" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B93" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A94" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B94" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B95" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A96" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B96" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B97" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B98" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B99" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B100" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B101" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B102" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>193</v>
+      </c>
+      <c r="B103" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>188</v>
+      </c>
+      <c r="B104" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>189</v>
+      </c>
+      <c r="B105" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>190</v>
+      </c>
+      <c r="B106" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>191</v>
+      </c>
+      <c r="B107" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B108" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B109" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B110" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B111" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B112" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B113" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B114" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B115" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B116" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>186</v>
+      </c>
+      <c r="B117" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>198</v>
+      </c>
+      <c r="B118" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>200</v>
+      </c>
+      <c r="B119" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>201</v>
+      </c>
+      <c r="B120" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>202</v>
+      </c>
+      <c r="B121" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B83" xr:uid="{1F7FE5DE-51AC-4617-BB94-0E66FF4A7B9B}"/>
+  <autoFilter ref="A1:B118" xr:uid="{1F7FE5DE-51AC-4617-BB94-0E66FF4A7B9B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B88">
+    <sortCondition ref="A1:A88"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/diccionario.xlsx
+++ b/diccionario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Indatech\Desktop\Sistema Automatizacion Finanzas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993FF303-6F2C-4DC8-9EE2-2DC4A2A1FB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C3FF46-4F9A-459C-A0F3-487B363BF092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{A9583FC7-4D3D-4BDA-AE3D-8A8227054763}"/>
+    <workbookView xWindow="-20610" yWindow="795" windowWidth="20730" windowHeight="11160" xr2:uid="{A9583FC7-4D3D-4BDA-AE3D-8A8227054763}"/>
   </bookViews>
   <sheets>
     <sheet name="CATEGORIA" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="204">
   <si>
     <t xml:space="preserve">SALDO INICIAL </t>
   </si>
@@ -651,6 +651,9 @@
   </si>
   <si>
     <t>COMPRA SIM CARD</t>
+  </si>
+  <si>
+    <t>DIETA DIRECTORES</t>
   </si>
 </sst>
 </file>
@@ -1151,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE9443F-E15E-4C56-A6CD-A01660DB3178}">
-  <dimension ref="A1:C123"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="158.5703125" style="10" customWidth="1"/>
@@ -2144,6 +2147,14 @@
       </c>
       <c r="B123" s="24" t="s">
         <v>167</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B124" s="10" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2158,7 +2169,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F7FE5DE-51AC-4617-BB94-0E66FF4A7B9B}">
-  <dimension ref="A1:B121"/>
+  <dimension ref="A1:B122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="74.42578125" customWidth="1"/>
@@ -3130,6 +3141,14 @@
         <v>48</v>
       </c>
     </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>203</v>
+      </c>
+      <c r="B122" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B118" xr:uid="{1F7FE5DE-51AC-4617-BB94-0E66FF4A7B9B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B88">
